--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_35.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1728492.386273654</v>
+        <v>1720546.743957416</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747601</v>
+        <v>7155604.990343563</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747601</v>
+        <v>7155604.990343563</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097731</v>
+        <v>1428532.779235607</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097731</v>
+        <v>1428532.779235607</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18751487.34853293</v>
+        <v>18747436.7118848</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>92.50795918773906</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>272.1216734720614</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>293.2016957795422</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S5" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>127.8837310637179</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>147.2737972923793</v>
+        <v>385</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>148.3468959953215</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>385</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>33.59582009342634</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
@@ -1182,7 +1182,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>215.3817731139785</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323.546446847424</v>
+        <v>148.6880250402009</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>340.7767994885277</v>
+        <v>118.4943215061023</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S14" t="n">
         <v>269.8481678023229</v>
@@ -1659,7 +1659,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V14" t="n">
         <v>404.8510241668239</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>142.2291713307485</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V17" t="n">
         <v>404.8510241668239</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.4925055126944</v>
+        <v>257.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>225.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>186.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>180.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>180.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>179.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>184.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>26.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>270.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>362.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>425.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>405.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>432.0322685380671</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>368.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>287.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>159.5565566463266</v>
+        <v>160.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>136.0999124455193</v>
+        <v>137.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>122.9376868977026</v>
+        <v>123.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>117.6720972219126</v>
+        <v>118.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>114.6362423378769</v>
+        <v>115.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>100.7395358750273</v>
+        <v>101.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>107.1680871864211</v>
+        <v>108.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>322.2737972923793</v>
+        <v>323.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>241.5639999646113</v>
+        <v>242.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>180.3577652175138</v>
+        <v>181.3577652175138</v>
       </c>
       <c r="U27" t="n">
-        <v>175.2103597601867</v>
+        <v>176.2103597601867</v>
       </c>
       <c r="V27" t="n">
-        <v>189.5106671915202</v>
+        <v>190.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>207.3731429098285</v>
+        <v>208.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>194.8627394453875</v>
+        <v>195.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>174.3913927661343</v>
+        <v>175.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>61.53621805555548</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>4.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2753,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>272.3400814329721</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>2.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>142.2291713307485</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>256.9993129555745</v>
+        <v>262.4925055126944</v>
       </c>
       <c r="C32" t="n">
         <v>224.4745782429939</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>3.77112610161862</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>60.0714981521398</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3397,10 +3397,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
@@ -3409,7 +3409,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>270.3153174799449</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3753,7 +3753,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3817,7 +3817,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096173</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3877,7 +3877,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>69.86273944538755</v>
@@ -3972,28 +3972,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>131.9993129555745</v>
+        <v>132.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>99.47457824299391</v>
+        <v>100.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>60.33915573984979</v>
+        <v>61.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>54.36328960686865</v>
+        <v>55.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>54.88962870801186</v>
+        <v>55.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>53.75737228701621</v>
+        <v>54.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>59.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>145.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>236.6755817285639</v>
+        <v>237.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>299.2212965486107</v>
+        <v>290.186687934025</v>
       </c>
       <c r="V44" t="n">
-        <v>279.8510241668239</v>
+        <v>280.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>288.3734759809475</v>
+        <v>289.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>242.2818334606677</v>
+        <v>243.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>161.3174326828064</v>
+        <v>162.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>35.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>11.09991244551929</v>
+        <v>65.77767497096187</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4102,25 +4102,25 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>179.2417624900537</v>
+        <v>117.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>56.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>51.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>65.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>83.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>69.86273944538755</v>
+        <v>70.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>50.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>73.54762815777917</v>
+        <v>58.49970300326394</v>
       </c>
       <c r="M46" t="n">
-        <v>170.6316114025499</v>
+        <v>171.6316114025499</v>
       </c>
       <c r="N46" t="n">
-        <v>221.1850752716849</v>
+        <v>222.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>290.445564079015</v>
+        <v>291.445564079015</v>
       </c>
       <c r="P46" t="n">
-        <v>337.4478973282775</v>
+        <v>338.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>375.839266425598</v>
+        <v>376.839266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>376.6021279811511</v>
+        <v>377.6021279811511</v>
       </c>
       <c r="S46" t="n">
-        <v>12.37347970285543</v>
+        <v>13.37347970285543</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>111.8101851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>61.83586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>51.39227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>46.98490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.04588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.25056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.16</v>
       </c>
       <c r="I2" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="K2" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="L2" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>403.39</v>
       </c>
       <c r="N2" t="n">
-        <v>793.0999999999999</v>
+        <v>776.6200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1174.25</v>
+        <v>1149.85</v>
       </c>
       <c r="P2" t="n">
-        <v>1174.25</v>
+        <v>1149.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1540</v>
+        <v>1508</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1508.000000000002</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1414.557616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1225.996423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.2577399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.0849882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.3036993811277</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.079625178433</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>194.6377739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>595.6130132457183</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>595.6130132457183</v>
       </c>
       <c r="D3" t="n">
-        <v>897.189519579215</v>
+        <v>595.6130132457183</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>249.4795817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>249.4795817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>249.4795817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>249.4795817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="J3" t="n">
-        <v>154.756520175299</v>
+        <v>154.1165201752989</v>
       </c>
       <c r="K3" t="n">
-        <v>343.9493362696824</v>
+        <v>343.3093362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>615.2997978648825</v>
+        <v>614.6597978648824</v>
       </c>
       <c r="M3" t="n">
-        <v>701.3803396077418</v>
+        <v>700.7403396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>834.6606242153101</v>
+        <v>834.02062421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.063075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1186.232420368536</v>
+        <v>1185.592420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1010.764879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>735.8945026285952</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>668.6581390279778</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>663.246254969883</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>663.0337703636337</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>648.3765307762396</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>615.6763864228775</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>595.6130132457183</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>595.6130132457183</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>341.0306935649782</v>
+        <v>593.2013882700642</v>
       </c>
       <c r="C4" t="n">
-        <v>467.032699383414</v>
+        <v>719.2033940885</v>
       </c>
       <c r="D4" t="n">
-        <v>467.032699383414</v>
+        <v>832.5225382135001</v>
       </c>
       <c r="E4" t="n">
-        <v>584.861603594827</v>
+        <v>950.3514424249131</v>
       </c>
       <c r="F4" t="n">
-        <v>709.2225761867625</v>
+        <v>1074.712415016849</v>
       </c>
       <c r="G4" t="n">
-        <v>709.2225761867625</v>
+        <v>1228.118980903734</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>1397.635566063132</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1397.635566063132</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1397.635566063132</v>
       </c>
       <c r="K4" t="n">
-        <v>1540</v>
+        <v>1508</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1484.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1362.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1189.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>946.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>656.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>360.0611393749001</v>
       </c>
       <c r="R4" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="U4" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="V4" t="n">
-        <v>229.621392885946</v>
+        <v>47.11304064086886</v>
       </c>
       <c r="W4" t="n">
-        <v>229.621392885946</v>
+        <v>219.0039589005463</v>
       </c>
       <c r="X4" t="n">
-        <v>229.621392885946</v>
+        <v>370.0347499247398</v>
       </c>
       <c r="Y4" t="n">
-        <v>341.0306935649782</v>
+        <v>481.444050603772</v>
       </c>
     </row>
     <row r="5">
@@ -4558,19 +4558,19 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K5" t="n">
-        <v>793.0999999999999</v>
+        <v>396.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1158.85</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>1158.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4582,7 +4582,7 @@
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S5" t="n">
         <v>1415.197616982083</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="C6" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="D6" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="E6" t="n">
-        <v>593.1864931608338</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4661,28 +4661,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>622.5159909842129</v>
       </c>
       <c r="S6" t="n">
-        <v>795.4071048660406</v>
+        <v>472.6706414939891</v>
       </c>
       <c r="T6" t="n">
-        <v>789.9952208079459</v>
+        <v>467.2587574358944</v>
       </c>
       <c r="U6" t="n">
-        <v>789.7827362016966</v>
+        <v>467.0462728296451</v>
       </c>
       <c r="V6" t="n">
-        <v>775.1254966143025</v>
+        <v>452.3890332422511</v>
       </c>
       <c r="W6" t="n">
-        <v>742.4253522609404</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="X6" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>722.3619790837812</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="7">
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="V7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="W7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="X7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="Y7" t="n">
-        <v>30.8</v>
+        <v>42.98476868153026</v>
       </c>
     </row>
     <row r="8">
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
         <v>42.68588988943799</v>
@@ -4795,22 +4795,22 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>411.9499999999999</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="M8" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="N8" t="n">
         <v>777.6999999999999</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>777.6999999999999</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1158.85</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
         <v>1158.85</v>
@@ -4825,22 +4825,22 @@
         <v>1444.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>395.5473863086054</v>
+        <v>746.9995952961838</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>789.7827362016966</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>775.1254966143025</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>742.4253522609404</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>722.3619790837812</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>722.3619790837812</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.98476868153026</v>
+        <v>404.9974293695179</v>
       </c>
       <c r="C10" t="n">
-        <v>168.986774499966</v>
+        <v>530.9994351879537</v>
       </c>
       <c r="D10" t="n">
-        <v>282.3059186249661</v>
+        <v>644.3185793129538</v>
       </c>
       <c r="E10" t="n">
-        <v>400.1348228363792</v>
+        <v>762.1474835243669</v>
       </c>
       <c r="F10" t="n">
-        <v>524.4957954283146</v>
+        <v>886.5084561163023</v>
       </c>
       <c r="G10" t="n">
-        <v>677.9023613151999</v>
+        <v>1039.915022003188</v>
       </c>
       <c r="H10" t="n">
-        <v>847.4189464745974</v>
+        <v>1209.431607162585</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.55182541068</v>
+        <v>1430.564486098668</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
@@ -4995,10 +4995,10 @@
         <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>30.8</v>
+        <v>181.8307910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>30.8</v>
+        <v>293.2400917032258</v>
       </c>
     </row>
     <row r="11">
@@ -5032,25 +5032,25 @@
         <v>81.36</v>
       </c>
       <c r="J11" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K11" t="n">
-        <v>645.2597178520556</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L11" t="n">
-        <v>1552.289212421678</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M11" t="n">
-        <v>2063.138041150613</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N11" t="n">
-        <v>2676.358360925376</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O11" t="n">
-        <v>3629.400904947332</v>
+        <v>3775.207553443145</v>
       </c>
       <c r="P11" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q11" t="n">
         <v>4068</v>
@@ -5108,19 +5108,19 @@
         <v>81.36</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L12" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N12" t="n">
         <v>1802.941204729126</v>
@@ -5166,55 +5166,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="C13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="D13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="E13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="F13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="G13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
       <c r="H13" t="n">
-        <v>189.862369793817</v>
+        <v>104.0957048649584</v>
       </c>
       <c r="I13" t="n">
-        <v>237.7452487298999</v>
+        <v>151.9785838010414</v>
       </c>
       <c r="J13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="K13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="L13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="M13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="N13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="O13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="P13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="Q13" t="n">
-        <v>425.5789893823512</v>
+        <v>339.8123244534927</v>
       </c>
       <c r="R13" t="n">
-        <v>81.36</v>
+        <v>220.1210906089449</v>
       </c>
       <c r="S13" t="n">
         <v>81.36</v>
@@ -5232,10 +5232,10 @@
         <v>193.6715880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>193.6715880782802</v>
+        <v>171.0012391589796</v>
       </c>
       <c r="Y13" t="n">
-        <v>193.6715880782802</v>
+        <v>107.9049231494217</v>
       </c>
     </row>
     <row r="14">
@@ -5272,16 +5272,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>645.2597178520556</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1552.289212421678</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M14" t="n">
-        <v>2063.138041150613</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N14" t="n">
-        <v>2676.358360925376</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O14" t="n">
         <v>3629.400904947332</v>
@@ -5293,13 +5293,13 @@
         <v>4068</v>
       </c>
       <c r="R14" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S14" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T14" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U14" t="n">
         <v>2969.902184378877</v>
@@ -5345,28 +5345,28 @@
         <v>81.36</v>
       </c>
       <c r="I15" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J15" t="n">
-        <v>232.0371006891147</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>643.9799167834981</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>1138.080378378698</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M15" t="n">
-        <v>1446.910920121557</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N15" t="n">
-        <v>1802.941204729126</v>
+        <v>1998.97062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P15" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q15" t="n">
         <v>2651.414528442776</v>
@@ -5433,22 +5433,22 @@
         <v>425.5789893823512</v>
       </c>
       <c r="L16" t="n">
-        <v>425.5789893823512</v>
+        <v>225.0258296270187</v>
       </c>
       <c r="M16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="N16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="O16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R16" t="n">
         <v>81.36</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G17" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H17" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
@@ -5509,16 +5509,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>645.2597178520556</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1552.289212421678</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M17" t="n">
-        <v>2063.138041150613</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N17" t="n">
-        <v>2676.358360925376</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O17" t="n">
         <v>3629.400904947332</v>
@@ -5539,19 +5539,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U17" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W17" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X17" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y17" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="18">
@@ -5585,10 +5585,10 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J18" t="n">
-        <v>232.0371006891147</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L18" t="n">
         <v>1138.080378378698</v>
@@ -5743,25 +5743,25 @@
         <v>81.36</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K20" t="n">
-        <v>645.2597178520556</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L20" t="n">
-        <v>1552.289212421678</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M20" t="n">
-        <v>2063.138041150613</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N20" t="n">
-        <v>2676.358360925376</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O20" t="n">
-        <v>3629.400904947332</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P20" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q20" t="n">
         <v>4068</v>
@@ -5919,10 +5919,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R22" t="n">
         <v>81.36</v>
@@ -5986,7 +5986,7 @@
         <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1201.550077243506</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M23" t="n">
         <v>1201.550077243506</v>
@@ -6056,25 +6056,25 @@
         <v>81.36</v>
       </c>
       <c r="I24" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J24" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>1341.904675832448</v>
+        <v>1334.109797864882</v>
       </c>
       <c r="M24" t="n">
-        <v>1650.735217575307</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O24" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P24" t="n">
         <v>2600.013000882351</v>
@@ -6156,10 +6156,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P25" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q25" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R25" t="n">
         <v>81.36</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1223.616245745725</v>
+        <v>1230.236851806331</v>
       </c>
       <c r="C26" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.484752570984</v>
       </c>
       <c r="D26" t="n">
-        <v>809.6629790963881</v>
+        <v>814.2633831367921</v>
       </c>
       <c r="E26" t="n">
-        <v>628.48793908945</v>
+        <v>632.078242119753</v>
       </c>
       <c r="F26" t="n">
-        <v>446.7812434247916</v>
+        <v>449.3614454449936</v>
       </c>
       <c r="G26" t="n">
-        <v>266.2182411146742</v>
+        <v>267.7883421247752</v>
       </c>
       <c r="H26" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="I26" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="J26" t="n">
-        <v>472.6691130376557</v>
+        <v>473.2291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1182.375479385524</v>
+        <v>1157.300343567238</v>
       </c>
       <c r="L26" t="n">
-        <v>2089.404973955146</v>
+        <v>1157.300343567238</v>
       </c>
       <c r="M26" t="n">
-        <v>2600.253802684082</v>
+        <v>1668.149172296173</v>
       </c>
       <c r="N26" t="n">
-        <v>3213.474122458845</v>
+        <v>2281.369492070936</v>
       </c>
       <c r="O26" t="n">
-        <v>3629.400904947332</v>
+        <v>3234.412036092893</v>
       </c>
       <c r="P26" t="n">
-        <v>3629.400904947332</v>
+        <v>4096</v>
       </c>
       <c r="Q26" t="n">
-        <v>4068</v>
+        <v>4096</v>
       </c>
       <c r="R26" t="n">
-        <v>4041.860001183541</v>
+        <v>4068.84990017344</v>
       </c>
       <c r="S26" t="n">
-        <v>3769.286094312508</v>
+        <v>3795.265892292306</v>
       </c>
       <c r="T26" t="n">
-        <v>3403.957223879615</v>
+        <v>3428.926920849312</v>
       </c>
       <c r="U26" t="n">
-        <v>2975.450863729503</v>
+        <v>2999.410459689099</v>
       </c>
       <c r="V26" t="n">
-        <v>2566.510435278165</v>
+        <v>2589.459930227661</v>
       </c>
       <c r="W26" t="n">
-        <v>2148.961469640845</v>
+        <v>2153.063699381128</v>
       </c>
       <c r="X26" t="n">
-        <v>1777.969718670473</v>
+        <v>1781.061847400656</v>
       </c>
       <c r="Y26" t="n">
-        <v>1488.760190708043</v>
+        <v>1490.842218428124</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>787.6767292570302</v>
+        <v>794.2973353176363</v>
       </c>
       <c r="C27" t="n">
-        <v>650.2020702211521</v>
+        <v>655.8125752716572</v>
       </c>
       <c r="D27" t="n">
-        <v>526.022588506301</v>
+        <v>530.6229925467051</v>
       </c>
       <c r="E27" t="n">
-        <v>407.1618842417428</v>
+        <v>410.7521872720458</v>
       </c>
       <c r="F27" t="n">
-        <v>291.3677000620692</v>
+        <v>293.9479020822712</v>
       </c>
       <c r="G27" t="n">
-        <v>189.6105931175971</v>
+        <v>191.1806941276981</v>
       </c>
       <c r="H27" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="I27" t="n">
-        <v>89.15487796756496</v>
+        <v>81.92</v>
       </c>
       <c r="J27" t="n">
-        <v>435.8613981428639</v>
+        <v>427.636520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>847.8042142372474</v>
+        <v>838.5893362696825</v>
       </c>
       <c r="L27" t="n">
-        <v>1341.904675832448</v>
+        <v>1331.699797864883</v>
       </c>
       <c r="M27" t="n">
-        <v>1650.735217575307</v>
+        <v>1639.540339607742</v>
       </c>
       <c r="N27" t="n">
-        <v>2006.765502182875</v>
+        <v>1994.58062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2468.557953866594</v>
+        <v>2455.383075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>2600.013000882351</v>
+        <v>2616.714516033866</v>
       </c>
       <c r="Q27" t="n">
-        <v>2651.414528442776</v>
+        <v>2667.126043594291</v>
       </c>
       <c r="R27" t="n">
-        <v>2325.885440268656</v>
+        <v>2340.58685441007</v>
       </c>
       <c r="S27" t="n">
-        <v>2081.881399900361</v>
+        <v>2095.572713031675</v>
       </c>
       <c r="T27" t="n">
-        <v>1899.70183907459</v>
+        <v>1912.383051195802</v>
       </c>
       <c r="U27" t="n">
-        <v>1722.721677700664</v>
+        <v>1734.392788811775</v>
       </c>
       <c r="V27" t="n">
-        <v>1531.296761345593</v>
+        <v>1541.957771446603</v>
       </c>
       <c r="W27" t="n">
-        <v>1321.828940224554</v>
+        <v>1331.479849315463</v>
       </c>
       <c r="X27" t="n">
-        <v>1124.997890279718</v>
+        <v>1133.638698360526</v>
       </c>
       <c r="Y27" t="n">
-        <v>948.8449682937237</v>
+        <v>956.4756753644309</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="C28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="D28" t="n">
-        <v>193.6715880782802</v>
+        <v>128.0936910524666</v>
       </c>
       <c r="E28" t="n">
-        <v>193.6715880782802</v>
+        <v>128.0936910524666</v>
       </c>
       <c r="F28" t="n">
-        <v>193.6715880782802</v>
+        <v>128.0936910524666</v>
       </c>
       <c r="G28" t="n">
-        <v>193.6715880782802</v>
+        <v>128.0936910524666</v>
       </c>
       <c r="H28" t="n">
-        <v>189.862369793817</v>
+        <v>123.2743717579023</v>
       </c>
       <c r="I28" t="n">
-        <v>237.7452487298999</v>
+        <v>170.1672506939852</v>
       </c>
       <c r="J28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="K28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="L28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="M28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="N28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="O28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="P28" t="n">
-        <v>425.5789893823512</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>357.0109913464365</v>
       </c>
       <c r="R28" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="S28" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="T28" t="n">
-        <v>96.18567915880486</v>
+        <v>95.75567915880487</v>
       </c>
       <c r="U28" t="n">
-        <v>169.4868717970915</v>
+        <v>168.0668717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>195.0582646830375</v>
+        <v>192.6482646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="X28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="Y28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
     </row>
     <row r="29">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C29" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H29" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I29" t="n">
         <v>81.36</v>
@@ -6457,16 +6457,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>690.7012485145707</v>
+        <v>1643.743792536527</v>
       </c>
       <c r="M29" t="n">
-        <v>1201.550077243506</v>
+        <v>2154.592621265462</v>
       </c>
       <c r="N29" t="n">
-        <v>1814.770397018269</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="O29" t="n">
         <v>2767.812941040225</v>
@@ -6487,19 +6487,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V29" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W29" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X29" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y29" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="30">
@@ -6539,13 +6539,13 @@
         <v>840.0093362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>1998.97062421531</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O30" t="n">
         <v>2264.733656412845</v>
@@ -6618,19 +6618,19 @@
         <v>425.5789893823512</v>
       </c>
       <c r="L31" t="n">
-        <v>225.0258296270187</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q31" t="n">
         <v>81.36</v>
@@ -6694,13 +6694,13 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>472.6691130376557</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L32" t="n">
-        <v>690.7012485145707</v>
+        <v>1303.921568289334</v>
       </c>
       <c r="M32" t="n">
-        <v>1201.550077243506</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="N32" t="n">
         <v>1814.770397018269</v>
@@ -6715,28 +6715,28 @@
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="33">
@@ -6770,25 +6770,25 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>283.4386282495398</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K33" t="n">
-        <v>695.3814443439232</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L33" t="n">
-        <v>1189.481905939123</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1498.312447681983</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1854.342732289551</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2316.13518397327</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
-        <v>2651.414528442776</v>
+        <v>2600.013000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>2651.414528442776</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>130.9303756165846</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C34" t="n">
-        <v>130.9303756165846</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D34" t="n">
-        <v>130.9303756165846</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>130.9303756165846</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F34" t="n">
-        <v>130.9303756165846</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G34" t="n">
-        <v>110.6840394130189</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
-        <v>106.8748211285556</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I34" t="n">
-        <v>154.7577000646385</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J34" t="n">
-        <v>342.5914407170899</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K34" t="n">
-        <v>342.5914407170899</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L34" t="n">
-        <v>142.0382809617574</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6919,34 +6919,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>64.92117127106515</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>618.3311712710652</v>
+        <v>733.1420762183974</v>
       </c>
       <c r="L35" t="n">
-        <v>1171.741171271065</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M35" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
         <v>44.72</v>
@@ -7040,19 +7040,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V36" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W36" t="n">
-        <v>274.6072361907175</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X36" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y36" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7116,10 +7116,10 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
         <v>521.9574820108303</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>927.106645136268</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>809.3652310305999</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>753.4482964674547</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>702.730761356155</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K40" t="n">
         <v>1921.561060958496</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
         <v>44.72</v>
@@ -7402,10 +7402,10 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>733.1420762183976</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L41" t="n">
         <v>733.1420762183976</v>
@@ -7429,25 +7429,25 @@
         <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="43">
@@ -7590,16 +7590,16 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
         <v>745.8791912947012</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>435.4610942305736</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>333.9716212578525</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>272.012878086287</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>216.0903633318742</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>159.636192919741</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>104.3257158621489</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,22 +7642,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>1171.741171271065</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2088.678618381492</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1848.602273201124</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1555.484406601099</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1271.796503402287</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>979.5000630174916</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>733.7608372996453</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>569.8038345897398</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>111.1620959302645</v>
       </c>
       <c r="C45" t="n">
         <v>44.72</v>
@@ -7745,25 +7745,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>466.2983195781991</v>
+        <v>528.5990898059188</v>
       </c>
       <c r="T45" t="n">
-        <v>410.3813850150538</v>
+        <v>471.6720542326725</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>419.9444181112718</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>353.7720270087261</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>269.5567311402125</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>197.9782064479018</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>147.0778097144328</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>870.8266123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>946.3386181306686</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1009.167762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1076.506666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1150.377639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1253.294204945902</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1372.3207901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1542.963669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1853.557409693834</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1913.431843630703</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1854.341234536497</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1680.975970493517</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1456.546601532219</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1162.157142866547</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>820.2905799086914</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>439.6448562464712</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>58.22856535641963</v>
       </c>
       <c r="S46" t="n">
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>182.3056791588048</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>378.3668717970914</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>526.6982646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>648.0991829427148</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>748.6399739669083</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>809.5592746459406</v>
       </c>
     </row>
   </sheetData>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>929.2621276423173</v>
+        <v>921.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>854.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>447.2478695740924</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>542.2671287719298</v>
+        <v>534.5903610951621</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>384.9999999999999</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="L5" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q8" t="n">
         <v>557.8226843274854</v>
@@ -8675,10 +8675,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
         <v>916.1914086561842</v>
@@ -8693,10 +8693,10 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>296.0370060577065</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
         <v>916.1914086561842</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>1032.917105959907</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -9164,7 +9164,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>1032.917105959907</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>1032.917105959907</v>
+        <v>458.3761793434905</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>736.2433981877273</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>690.981040938972</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,13 +9875,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>220.2344802797121</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,7 +10112,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>870.5779326741233</v>
@@ -10337,16 +10337,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>220.2344802797121</v>
+        <v>122.773827175565</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
         <v>1032.917105959907</v>
@@ -10571,10 +10571,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>55.44822975121676</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
@@ -10583,7 +10583,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10592,7 +10592,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>300.1141042229715</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11285,10 +11285,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>184.1434931650599</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.340208614583844</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>32.63757064605574</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23429,10 +23429,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8253284926234</v>
+        <v>383.1078064750487</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23447,10 +23447,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23648,10 +23648,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>295.6316114025499</v>
+        <v>153.4024400718014</v>
       </c>
       <c r="N16" t="n">
         <v>346.1850752716849</v>
@@ -23666,7 +23666,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>137.3734797028554</v>
@@ -24134,13 +24134,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q22" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S22" t="n">
         <v>137.3734797028554</v>
@@ -24371,13 +24371,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q25" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24566,22 +24566,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>63.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>48.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>55.98090483695654</v>
+        <v>56.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>50.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>21.04387284153003</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24593,31 +24593,31 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>64.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>199.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>296.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>347.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>415.445564079015</v>
+        <v>416.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>462.4478973282775</v>
+        <v>463.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370703</v>
+        <v>501.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>230.2620465481789</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>138.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,10 +24632,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>23.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>63.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24833,10 +24833,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>153.4024400718014</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>346.1850752716849</v>
@@ -24848,7 +24848,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R31" t="n">
         <v>501.6021279811511</v>
@@ -25040,7 +25040,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C34" t="n">
         <v>47.72524664804467</v>
@@ -25055,7 +25055,7 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -25070,10 +25070,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>235.5601132504101</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>346.1850752716849</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25887,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>10.03460861458564</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>16.04792515451523</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1157099.39426644</v>
+        <v>1155906.203730374</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259020.889973892</v>
+        <v>2258205.920043887</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3360942.385681347</v>
+        <v>3360127.415751341</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4430585.044896968</v>
+        <v>4429770.074966962</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5470348.276233801</v>
+        <v>5469533.306303795</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6510111.507570631</v>
+        <v>6509296.537640626</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7549874.738907457</v>
+        <v>7549059.768977452</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8589637.970244285</v>
+        <v>8588823.00031428</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9629401.201581113</v>
+        <v>9628415.264181409</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10669164.43291794</v>
+        <v>10667847.55248794</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11708927.66425477</v>
+        <v>11707610.78382476</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12789229.44484882</v>
+        <v>12787912.56441882</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13891184.35513985</v>
+        <v>13889867.47470985</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14993139.26543088</v>
+        <v>14991822.38500088</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16095094.17572191</v>
+        <v>16092741.37837365</v>
       </c>
     </row>
   </sheetData>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1101106.525777448</v>
+      </c>
+      <c r="C2" t="n">
         <v>1101921.495707453</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1101921.495707454</v>
       </c>
       <c r="D2" t="n">
         <v>1101921.495707453</v>
@@ -26281,7 +26281,7 @@
         <v>1039763.231336833</v>
       </c>
       <c r="F2" t="n">
-        <v>1039763.231336833</v>
+        <v>1039763.231336832</v>
       </c>
       <c r="G2" t="n">
         <v>1039763.231336833</v>
@@ -26290,19 +26290,19 @@
         <v>1039763.231336833</v>
       </c>
       <c r="I2" t="n">
+        <v>1039763.231336832</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1039261.320836833</v>
+      </c>
+      <c r="K2" t="n">
         <v>1039763.231336833</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1039763.231336833</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1039763.231336832</v>
       </c>
       <c r="L2" t="n">
         <v>1039763.231336833</v>
       </c>
       <c r="M2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="N2" t="n">
         <v>1101954.910291021</v>
@@ -26311,7 +26311,7 @@
         <v>1101954.910291021</v>
       </c>
       <c r="P2" t="n">
-        <v>1101954.910291021</v>
+        <v>1100918.99337277</v>
       </c>
     </row>
     <row r="3">
@@ -26321,10 +26321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135520</v>
+        <v>132704</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315520</v>
+        <v>314368</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>180000</v>
+        <v>179200</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572894.2778066028</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.290050781</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121191</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>439748.2013963978</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464518</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>522671.0542953382</v>
       </c>
     </row>
     <row r="5">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57035.6</v>
+        <v>56549.2</v>
       </c>
       <c r="C5" t="n">
         <v>57035.6</v>
@@ -26449,7 +26449,7 @@
         <v>80749.125</v>
       </c>
       <c r="J5" t="n">
-        <v>80749.125</v>
+        <v>81090.656</v>
       </c>
       <c r="K5" t="n">
         <v>80749.125</v>
@@ -26467,7 +26467,7 @@
         <v>63411.35</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63327.281</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>338451.7708079444</v>
+        <v>338959.047970845</v>
       </c>
       <c r="C6" t="n">
-        <v>476029.7509417589</v>
+        <v>471697.8952534428</v>
       </c>
       <c r="D6" t="n">
-        <v>478090.5228540743</v>
+        <v>476574.6671657584</v>
       </c>
       <c r="E6" t="n">
-        <v>110697.4168249708</v>
+        <v>108360.7089132733</v>
       </c>
       <c r="F6" t="n">
-        <v>514614.9675886008</v>
+        <v>512278.2596769029</v>
       </c>
       <c r="G6" t="n">
-        <v>516070.5241977491</v>
+        <v>513733.8162860514</v>
       </c>
       <c r="H6" t="n">
-        <v>517528.101036411</v>
+        <v>515191.3931247136</v>
       </c>
       <c r="I6" t="n">
-        <v>518987.7126759975</v>
+        <v>516651.0047642996</v>
       </c>
       <c r="J6" t="n">
-        <v>204929.37387889</v>
+        <v>204054.4634404351</v>
       </c>
       <c r="K6" t="n">
-        <v>521913.0996020781</v>
+        <v>518424.3916903806</v>
       </c>
       <c r="L6" t="n">
-        <v>523378.9050008956</v>
+        <v>521042.197089198</v>
       </c>
       <c r="M6" t="n">
-        <v>349820.8357489196</v>
+        <v>348078.9859358121</v>
       </c>
       <c r="N6" t="n">
-        <v>513033.7327837738</v>
+        <v>511291.8829706656</v>
       </c>
       <c r="O6" t="n">
-        <v>335001.4720415116</v>
+        <v>334059.6222284037</v>
       </c>
       <c r="P6" t="n">
-        <v>516972.0748925216</v>
+        <v>514920.6580774316</v>
       </c>
     </row>
   </sheetData>
@@ -26779,7 +26779,7 @@
         <v>225</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
         <v>225</v>
@@ -26797,7 +26797,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C4" t="n">
         <v>385</v>
@@ -26883,7 +26883,7 @@
         <v>1017</v>
       </c>
       <c r="J4" t="n">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="K4" t="n">
         <v>1017</v>
@@ -26987,22 +26987,22 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>125</v>
@@ -27011,7 +27011,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27033,25 +27033,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>-0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>-0</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27228,10 +27228,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>250.878598828296</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>275.1521238203179</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,16 +27606,16 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>368.363419321654</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27651,13 +27651,13 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
+        <v>216.2945936918413</v>
+      </c>
+      <c r="W4" t="n">
         <v>400</v>
       </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S5" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27758,10 +27758,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>214.7883661581947</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>162.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>318.2171039692898</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>34.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>299.4216474901395</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>374.6813268559163</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
@@ -27919,7 +27919,7 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.01010979890259</v>
+        <v>235.8685316061257</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>299.4216474901395</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28089,10 +28089,10 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>145.809871968566</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28244,13 +28244,13 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>26.99048536749061</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28259,7 +28259,7 @@
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S14" t="n">
         <v>225</v>
@@ -28438,7 +28438,7 @@
         <v>225</v>
       </c>
       <c r="U14" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V14" t="n">
         <v>225</v>
@@ -28481,10 +28481,10 @@
         <v>225</v>
       </c>
       <c r="I15" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K15" t="n">
         <v>225</v>
@@ -28499,13 +28499,13 @@
         <v>225</v>
       </c>
       <c r="O15" t="n">
-        <v>225</v>
+        <v>78.91122027701093</v>
       </c>
       <c r="P15" t="n">
         <v>225</v>
       </c>
       <c r="Q15" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>225</v>
@@ -28639,7 +28639,7 @@
         <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>225</v>
       </c>
       <c r="U17" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V17" t="n">
         <v>225</v>
@@ -28721,13 +28721,13 @@
         <v>225</v>
       </c>
       <c r="J18" t="n">
-        <v>19.11687125883914</v>
+        <v>225</v>
       </c>
       <c r="K18" t="n">
         <v>225</v>
       </c>
       <c r="L18" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M18" t="n">
         <v>225</v>
@@ -29192,7 +29192,7 @@
         <v>225</v>
       </c>
       <c r="I24" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>225</v>
@@ -29207,13 +29207,13 @@
         <v>225</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>26.99048536749072</v>
       </c>
       <c r="O24" t="n">
         <v>225</v>
       </c>
       <c r="P24" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q24" t="n">
         <v>225</v>
@@ -29329,25 +29329,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>219.5068074428801</v>
+        <v>224</v>
       </c>
       <c r="C26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I26" t="n">
         <v>150.0811596826846</v>
@@ -29377,28 +29377,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W26" t="n">
-        <v>225</v>
+        <v>206.3412074428804</v>
       </c>
       <c r="X26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
@@ -29408,76 +29408,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P27" t="n">
-        <v>19.11687125883908</v>
+        <v>49.29504612659638</v>
       </c>
       <c r="Q27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
@@ -29587,7 +29587,7 @@
         <v>225</v>
       </c>
       <c r="I29" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29623,7 +29623,7 @@
         <v>225</v>
       </c>
       <c r="U29" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V29" t="n">
         <v>225</v>
@@ -29675,7 +29675,7 @@
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>26.99048536749063</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
@@ -29684,7 +29684,7 @@
         <v>225</v>
       </c>
       <c r="O30" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="P30" t="n">
         <v>225</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="C32" t="n">
         <v>225</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29906,7 +29906,7 @@
         <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>71.03760616835949</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
@@ -29927,7 +29927,7 @@
         <v>225</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R33" t="n">
         <v>225</v>
@@ -30055,13 +30055,13 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30176,10 +30176,10 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
+        <v>287.3222374745575</v>
+      </c>
+      <c r="V36" t="n">
         <v>350</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
@@ -30188,7 +30188,7 @@
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30252,13 +30252,13 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
       </c>
       <c r="V37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W37" t="n">
         <v>350</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>285.2599243722601</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30532,7 +30532,7 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30596,7 +30596,7 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -30641,10 +30641,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30656,7 +30656,7 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30751,28 +30751,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,25 +30802,25 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45">
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>295.3222374745574</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30881,25 +30881,25 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>287.3222374745576</v>
+        <v>349</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>349</v>
       </c>
       <c r="U46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -34752,22 +34752,22 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N2" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>369.4444444444445</v>
+        <v>361.7676767676766</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.607692654649116e-12</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,16 +34892,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>139.5922932200353</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34937,13 +34937,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>17.12428347562511</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,22 +34980,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>369.4444444444445</v>
+      </c>
+      <c r="L5" t="n">
         <v>385</v>
       </c>
-      <c r="K5" t="n">
-        <v>384.9999999999999</v>
-      </c>
-      <c r="L5" t="n">
-        <v>369.4444444444443</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.30784715306086</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>12.30784715306086</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>385</v>
-      </c>
-      <c r="L8" t="n">
-        <v>369.4444444444445</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>385</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>385</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.30784715306086</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35375,10 +35375,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>110.5409231326582</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35417,10 +35417,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
         <v>916.1914086561842</v>
@@ -35472,10 +35472,10 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>295.7499460170251</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>218.0943400082819</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35545,7 +35545,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
         <v>916.1914086561842</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>962.6692363858147</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35767,10 +35767,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K15" t="n">
         <v>416.1038546407913</v>
@@ -35785,13 +35785,13 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>466.4570219027464</v>
+        <v>320.3682421797573</v>
       </c>
       <c r="P15" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -35943,7 +35943,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>962.6692363858147</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36007,13 +36007,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J18" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M18" t="n">
         <v>311.9500421645043</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>174.3339442569695</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>962.6692363858147</v>
+        <v>388.1283097693981</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36408,10 +36408,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>736.2433981877273</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>350.2086062376757</v>
@@ -36493,13 +36493,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>161.6170354761456</v>
       </c>
       <c r="O24" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>51.92073490952041</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230996</v>
+        <v>690.981040938972</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,13 +36654,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,31 +36715,31 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>349.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>416.1038546407913</v>
+        <v>415.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>498.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>310.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>358.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>465.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>132.7828757734923</v>
+        <v>162.9610506412496</v>
       </c>
       <c r="Q27" t="n">
-        <v>51.92073490952041</v>
+        <v>50.92073490952041</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,10 +36794,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>48.36654437988173</v>
+        <v>47.36654437988173</v>
       </c>
       <c r="J28" t="n">
-        <v>189.7310511640922</v>
+        <v>188.7310511640922</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -36827,13 +36827,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>14.97543349374229</v>
+        <v>13.97543349374229</v>
       </c>
       <c r="U28" t="n">
-        <v>74.04160872554206</v>
+        <v>73.04160872554206</v>
       </c>
       <c r="V28" t="n">
-        <v>25.82968978378381</v>
+        <v>24.82968978378381</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>220.2344802797121</v>
+        <v>466.0285991424271</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,7 +36891,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>870.2908726334418</v>
@@ -36961,7 +36961,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>499.091375348687</v>
+        <v>301.0818607161776</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
@@ -36970,7 +36970,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>268.4475072702369</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
         <v>338.6660045146532</v>
@@ -37116,16 +37116,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L32" t="n">
-        <v>220.2344802797121</v>
+        <v>122.773827175565</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>962.6692363858147</v>
@@ -37192,7 +37192,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>196.2462124060352</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
@@ -37213,7 +37213,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,10 +37350,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>20.40522350612643</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
@@ -37362,7 +37362,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,13 +37538,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W37" t="n">
         <v>123.6271901612903</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>300.1141042229715</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38064,10 +38064,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>184.1434931650599</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38195,34 +38195,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62.88619966292134</v>
+        <v>61.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>77.27475335195533</v>
+        <v>76.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>64.46378194444452</v>
+        <v>63.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>69.01909516304346</v>
+        <v>68.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>75.61714403225807</v>
+        <v>74.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>104.95612715847</v>
+        <v>103.95612715847</v>
       </c>
       <c r="H46" t="n">
-        <v>121.2288738983814</v>
+        <v>120.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>172.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>313.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>60.47922619885696</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,22 +38249,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>138.9754334937423</v>
       </c>
       <c r="U46" t="n">
-        <v>199.0416087255421</v>
+        <v>198.0416087255421</v>
       </c>
       <c r="V46" t="n">
-        <v>150.8296897837838</v>
+        <v>149.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>123.6271901612903</v>
+        <v>122.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>102.5563545698924</v>
+        <v>101.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>62.53464715053764</v>
+        <v>61.53464715053764</v>
       </c>
     </row>
   </sheetData>
